--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79000</v>
+        <v>79001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131107106</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131107106</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131107106</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131107106</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>131107103</v>
       </c>
       <c r="B5" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131107106</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17268349</v>
+        <v>131107143</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sothammaren, Mpd</t>
+          <t>SÖ Svarttjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600261.1887348457</v>
+        <v>600294</v>
       </c>
       <c r="R2" t="n">
-        <v>6952287.702554088</v>
+        <v>6952166</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,54 +738,59 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2025_0024</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning pga dålig fältlupp</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
+          <t>Erik Lagerin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>
@@ -803,7 +799,7 @@
         <v>131107108</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131107106</v>
+        <v>131107138</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,26 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600259</v>
+        <v>600300</v>
       </c>
       <c r="R4" t="n">
-        <v>6952247</v>
+        <v>6952163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +986,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0063</t>
+          <t>2025_0029</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -995,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt födosök av spillkråka</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131107103</v>
+        <v>131107106</v>
       </c>
       <c r="B5" t="n">
-        <v>8442</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,34 +1048,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>SÖ Svarttjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600292</v>
+        <v>600259</v>
       </c>
       <c r="R5" t="n">
-        <v>6952283</v>
+        <v>6952247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0066</t>
+          <t>2025_0063</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammalt födosök av spillkråka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1151,242 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131107103</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SÖ Svarttjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6952283</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2025_0066</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Erik Lagerin</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131107137</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SÖ Svarttjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600292</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6952170</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2025_0030</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 25117-2025 artfynd.xlsx
+++ b/artfynd/A 25117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107138</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107106</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1391,8 +1421,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131107137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>